--- a/output/full_scan/batch_seq1_2026-09-15.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-15.xlsx
@@ -4089,7 +4089,7 @@
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>249.0854031827182</v>
+        <v>249.0854031827181</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>25.8</v>
